--- a/reports/excel/698167220.xlsx
+++ b/reports/excel/698167220.xlsx
@@ -539,20 +539,20 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>The customer exhibits a relatively stable financial situation, with a balanced monthly cash flow and manageable expenses. Their spending categories include self-expenses, other expenses, food and restaurant bills, and a rent commitment, although the exact amount is not specified. The customer's income is steady, as evidenced by their recent salary receipt of ₹72,000 in Jun 2025, which was immediately transferred to their own account. This demonstrates discipline in managing their finances. However, there are some concerns regarding credit portfolio exposure, with a high sanctioned exposure of INR 72,48,130 and elevated credit card utilization at 9.0%. The customer's repayment profile is generally healthy, with no missed payments over the past 18 months and zero DPD across all products and windows. Overall, the customer's creditworthiness assessment is cautious due to the high credit portfolio exposure and moderate credit card utilization.
-Note: This is a synthesised summary based on automated banking and bureau analyses. Independent verification is recommended before final credit decisions.</t>
+          <t>The customer exhibits a relatively balanced financial situation, with a stable income and cash flow. Their monthly net is ₹18,000, indicating manageable expenses. The customer's spending categories reveal self-expenses of ₹48,000, other expenses of ₹27,300, and food bills of ₹1,970. Salary income from Symed averages ₹39,210 per month, received in two transactions. The customer's obligation-to-income ratio is comfortable, with a banking FOIR ratio of 0.0%. However, the credit portfolio exposure highlights a sanctioned exposure peak of ₹66.6L in February 2025, primarily driven by credit card and personal loan sanctions. Current exposure stands at ₹64.1L (CC, PL active), down 4% from peak, indicating a stable trend.
+Creditworthiness Assessment: The customer's overall financial profile suggests a cautious assessment due to over-leveraged FOIR percentages of 68.5% for the total portfolio and 60.8% for unsecured only, with exposure commentary indicating a decreasing trend in sanctioned exposure.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>The customer's tradeline portfolio consists of a total of 27 live and closed accounts, with 26 credit card accounts and 1 personal loan account. The sanctioned exposure is INR 72,48,130, with unsecured outstanding balances accounting for 100% of the total outstanding amount. Key highlights include a credit card utilization percentage of 9.0%, indicating moderate usage, and no missed payments over the past 18 months. Additionally, there are 5 closed credit card accounts, suggesting some churn in the portfolio.
-The customer's behavioral features indicate a relatively healthy repayment profile, with zero DPD across all products and windows, and no missed payments over the past 18 months. The credit card utilization is elevated at 9.0%, but this is still within the moderate range. The loan acquisition velocity is moderate, with an average interpurchase time of 3.45 months. However, there are some red flags, including [HIGH RISK] loan stacking indicated by 3 new personal loans in 6 months, and a high trade-to-enquiry ratio of 40.00%.</t>
+          <t>The customer's tradeline portfolio consists of a total of 27 live and closed tradelines, with 22 live tradelines and 5 closed ones. The portfolio is dominated by credit cards, with 26 accounts, while personal loans account for only one live account. The sanctioned exposure stands at INR 72,48,130, with unsecured sanction amount also being INR 72,48,130. The total outstanding amount is INR 8,22,679, with unsecured outstanding amount being 100% of the total outstanding. Key highlights include a credit card utilization percentage of 9.0%, no DPD values above zero, and missed payment percentages of 0.00%. Enquiry counts are minimal, with only 0 unsecured enquiries in the last 12 months. Loan acquisition velocity is moderate, with an average interpurchase time of 3.45 months for all loans.
+The customer's obligation &amp; FOIR highlights a total bureau EMI obligation of INR 47,937 and an unsecured EMI obligation of INR 42,537. Affluence income is estimated at INR 70,000. The FOIR percentages are 68.5% [OVER-LEVERAGED] for the total portfolio and 60.8% [STRETCHED] for unsecured only. Exposure commentary indicates a sanctioned exposure trend that has decreased by 4% over the last 12 months, from ₹66.6L to ₹64.1L, with a recent average of ₹64.3L. The peak exposure was INR 66.6L in February 2025, led by credit card and personal loan sanctions, but current exposure stands at ₹64.1L (CC, PL active), down 4% from peak — trend stable.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>The customer's banking profile indicates a stable financial situation. Their monthly cash flow is relatively balanced, with an average net of ₹18,000 and total inflows exceeding outflows by ₹37. The customer's key spending categories include self expenses at ₹48,000 per month, followed by other expenses at ₹27,300, and food and restaurant bills at ₹1,970. Additionally, the customer has a rent commitment, although the exact amount is not specified. Utility bills are also present in their monthly expenditure.
-In Jun 2025, the customer received ₹72,000 salary from Symed and transferred ₹72,000 to their own account the next day. In Jul 2025, the customer made a payment of ₹27,300 towards other expenses.</t>
+          <t>The customer's banking profile indicates a stable financial situation. Their monthly cash flow is relatively balanced, with an average net of ₹18,000 and total inflows exceeding total outflows by ₹37. The customer's key spending categories include self (₹48,000), other expenses (₹27,300), and food and restaurant bills (₹1,970). Their salary income comes from Symed, with an average amount of ₹39,210 per month, received in two transactions. The customer's banking FOIR ratio is 0.0%, indicating a comfortable obligation-to-income ratio.
+In Jun 2025, the customer received ₹72,000 salary and transferred ₹72,000 to their own account the next day. In Jul 2025, the customer made a payment of ₹27,300 towards other expenses.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">

--- a/reports/excel/698167220.xlsx
+++ b/reports/excel/698167220.xlsx
@@ -539,14 +539,16 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>The customer exhibits a relatively balanced financial situation, with a stable income and cash flow. Their monthly net is ₹18,000, indicating manageable expenses. The customer's spending categories reveal self-expenses of ₹48,000, other expenses of ₹27,300, and food bills of ₹1,970. Salary income from Symed averages ₹39,210 per month, received in two transactions. The customer's obligation-to-income ratio is comfortable, with a banking FOIR ratio of 0.0%. However, the credit portfolio exposure highlights a sanctioned exposure peak of ₹66.6L in February 2025, primarily driven by credit card and personal loan sanctions. Current exposure stands at ₹64.1L (CC, PL active), down 4% from peak, indicating a stable trend.
-Creditworthiness Assessment: The customer's overall financial profile suggests a cautious assessment due to over-leveraged FOIR percentages of 68.5% for the total portfolio and 60.8% for unsecured only, with exposure commentary indicating a decreasing trend in sanctioned exposure.</t>
+          <t>The customer exhibits a stable financial situation, with a balanced monthly cash flow and manageable spending categories. Their income from Symed is consistent, with a steady salary amount received in two transactions per month. The customer's credit portfolio consists of 27 live and closed accounts, primarily credit cards, with a sanctioned amount of ₹72,48,130 and an outstanding amount of ₹8,22,679. Unsecured exposure is equivalent to the total outstanding amount at 100%. Credit utilization stands at 9.0%, while the obligation-to-income ratio is comfortable at 0.0%. The customer's credit behavior is characterized by a clean repayment profile, with zero days past due and no missed payments. However, the personal loan balance remaining is significant at ₹53.46%. Overall, the customer's creditworthiness assessment is cautious.
+Note: This is a synthesised summary based on automated banking and bureau analyses. Independent verification is recommended before final credit decisions.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>The customer's tradeline portfolio consists of a total of 27 live and closed tradelines, with 22 live tradelines and 5 closed ones. The portfolio is dominated by credit cards, with 26 accounts, while personal loans account for only one live account. The sanctioned exposure stands at INR 72,48,130, with unsecured sanction amount also being INR 72,48,130. The total outstanding amount is INR 8,22,679, with unsecured outstanding amount being 100% of the total outstanding. Key highlights include a credit card utilization percentage of 9.0%, no DPD values above zero, and missed payment percentages of 0.00%. Enquiry counts are minimal, with only 0 unsecured enquiries in the last 12 months. Loan acquisition velocity is moderate, with an average interpurchase time of 3.45 months for all loans.
-The customer's obligation &amp; FOIR highlights a total bureau EMI obligation of INR 47,937 and an unsecured EMI obligation of INR 42,537. Affluence income is estimated at INR 70,000. The FOIR percentages are 68.5% [OVER-LEVERAGED] for the total portfolio and 60.8% [STRETCHED] for unsecured only. Exposure commentary indicates a sanctioned exposure trend that has decreased by 4% over the last 12 months, from ₹66.6L to ₹64.1L, with a recent average of ₹64.3L. The peak exposure was INR 66.6L in February 2025, led by credit card and personal loan sanctions, but current exposure stands at ₹64.1L (CC, PL active), down 4% from peak — trend stable.</t>
+          <t>Portfolio Overview:
+The tradeline portfolio consists of a total of 27 live and closed accounts, with credit card accounts making up 26 of these, and personal loan accounts comprising one. The sanctioned amount totals INR 72,48,130, while the outstanding amount is INR 8,22,679. Unsecured exposure is equivalent to the total outstanding amount at 100%. There are no days past due (DPD) recorded, with credit card utilization standing at 9.0%. The obligation and FOIR data indicates a total EMI obligation of INR 47,937, with unsecured EMI obligation at INR 42,537, and FOIR percentages of 68.5% for the total and 60.8% for the unsecured only. Sanctioned exposure has decreased by 4% over the last 12 months, from ₹66.6L to ₹64.1L, with a stable trend.
+Behavioral Insights:
+The customer's credit behavior is characterized by [CLEAN REPAYMENT PROFILE] across all products and windows, with zero DPD recorded and no missed payments. Credit card utilization is at 8.97%, indicating a [HEALTHY] balance. However, the personal loan balance remaining stands at 53.46%, which could be considered [MODERATE — significant PL balance remaining]. The customer has made minimal unsecured enquiries over the last 12 months, with a trade-to-enquiry ratio of 40.00%. The loan acquisition velocity is average, with an interpurchase time of 3.45 months.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">

--- a/reports/excel/698167220.xlsx
+++ b/reports/excel/698167220.xlsx
@@ -539,22 +539,21 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>The customer exhibits a stable financial situation, with a balanced monthly cash flow and manageable spending categories. Their income from Symed is consistent, with a steady salary amount received in two transactions per month. The customer's credit portfolio consists of 27 live and closed accounts, primarily credit cards, with a sanctioned amount of ₹72,48,130 and an outstanding amount of ₹8,22,679. Unsecured exposure is equivalent to the total outstanding amount at 100%. Credit utilization stands at 9.0%, while the obligation-to-income ratio is comfortable at 0.0%. The customer's credit behavior is characterized by a clean repayment profile, with zero days past due and no missed payments. However, the personal loan balance remaining is significant at ₹53.46%. Overall, the customer's creditworthiness assessment is cautious.
-Note: This is a synthesised summary based on automated banking and bureau analyses. Independent verification is recommended before final credit decisions.</t>
+          <t>The customer's banking profile indicates a stable financial situation. Their monthly cash flow is characterized by an average net inflow of ₹18, with total inflows exceeding outflows by ₹37. The customer's key spending categories include self expenses at ₹48,000, other expenses at ₹27,300, and food and restaurant expenditures at ₹1,970. Additionally, the customer has a relatively comfortable obligation-to-income ratio, as indicated by their Banking FOIR, which stands at 0.0% and is classified as comfortable.
+The customer's tradeline portfolio consists of N=27 total tradelines, M=22 live tradelines, and P=5 closed tradelines. The portfolio features a mix of credit card (26 accounts) and personal loan (1 account) products, with sanctioned exposure totaling INR 72,48,130 and outstanding balances of INR 8,22,679 for the entire portfolio, and INR 3,11,925 for the personal loan product. The customer's credit utilization percentage is 9.0% for credit cards, indicating a relatively healthy balance. Overall, this synthesised summary suggests a low-risk profile, with stable financial management and a manageable credit portfolio.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Portfolio Overview:
-The tradeline portfolio consists of a total of 27 live and closed accounts, with credit card accounts making up 26 of these, and personal loan accounts comprising one. The sanctioned amount totals INR 72,48,130, while the outstanding amount is INR 8,22,679. Unsecured exposure is equivalent to the total outstanding amount at 100%. There are no days past due (DPD) recorded, with credit card utilization standing at 9.0%. The obligation and FOIR data indicates a total EMI obligation of INR 47,937, with unsecured EMI obligation at INR 42,537, and FOIR percentages of 68.5% for the total and 60.8% for the unsecured only. Sanctioned exposure has decreased by 4% over the last 12 months, from ₹66.6L to ₹64.1L, with a stable trend.
-Behavioral Insights:
-The customer's credit behavior is characterized by [CLEAN REPAYMENT PROFILE] across all products and windows, with zero DPD recorded and no missed payments. Credit card utilization is at 8.97%, indicating a [HEALTHY] balance. However, the personal loan balance remaining stands at 53.46%, which could be considered [MODERATE — significant PL balance remaining]. The customer has made minimal unsecured enquiries over the last 12 months, with a trade-to-enquiry ratio of 40.00%. The loan acquisition velocity is average, with an interpurchase time of 3.45 months.</t>
+          <t>Here is the executive summary:
+The customer's tradeline portfolio consists of N=27 total tradelines, M=22 live tradelines, and P=5 closed tradelines. The portfolio features a mix of credit card (26 accounts) and personal loan (1 account) products, with sanctioned exposure totaling INR 72,48,130 and outstanding balances of INR 8,22,679 for the entire portfolio, and INR 3,11,925 for the personal loan product. The customer's credit utilization percentage is 9.0% for credit cards, indicating a relatively healthy balance. Notably, there are no DPD values above zero, suggesting a clean payment history.
+The customer's behavioral features indicate a low-risk profile. The % Missed Payments Last 18M is 0.00%, indicating no missed payments, and the Trade-to-Enquiry Ratio (Unsec 24M) is 40.00%, which is within healthy limits. The CC Balance Utilization is 8.97%, and the PL Balance Remaining is 53.46%, with the latter being moderate but not concerning. The customer has a low enquiry activity, with Unsecured Enquiries Last 12M at 0, indicating minimal enquiry pressure. The Avg Interpurchase Time All Loans (24M) is 3.45 months, suggesting a relatively stable loan acquisition velocity. Overall, the customer's credit behavior suggests a low-risk profile.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>The customer's banking profile indicates a stable financial situation. Their monthly cash flow is relatively balanced, with an average net of ₹18,000 and total inflows exceeding total outflows by ₹37. The customer's key spending categories include self (₹48,000), other expenses (₹27,300), and food and restaurant bills (₹1,970). Their salary income comes from Symed, with an average amount of ₹39,210 per month, received in two transactions. The customer's banking FOIR ratio is 0.0%, indicating a comfortable obligation-to-income ratio.
-In Jun 2025, the customer received ₹72,000 salary and transferred ₹72,000 to their own account the next day. In Jul 2025, the customer made a payment of ₹27,300 towards other expenses.</t>
+          <t>The customer's banking profile indicates a stable financial situation. Their monthly cash flow is characterized by an average net inflow of ₹18, with total inflows exceeding outflows by ₹37. The customer's key spending categories include self expenses at ₹48,000, other expenses at ₹27,300, and food and restaurant expenditures at ₹1,970. Additionally, the customer has a relatively comfortable obligation-to-income ratio, as indicated by their Banking FOIR, which stands at 0.0% and is classified as comfortable.
+There are no detected transaction events to report.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">

--- a/reports/excel/698167220.xlsx
+++ b/reports/excel/698167220.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,15 +506,25 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>Exposure Commentary</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>TU Score</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>Transaction Red flag</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Concerns</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Intelligent Report</t>
         </is>
@@ -525,22 +535,14 @@
         <v>698167220</v>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>39,210 / Symed</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Salary</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>The customer's banking profile indicates a stable financial situation. Their monthly cash flow is characterized by an average net inflow of ₹18, with total inflows exceeding outflows by ₹37. The customer's key spending categories include self expenses at ₹48,000, other expenses at ₹27,300, and food and restaurant expenditures at ₹1,970. Additionally, the customer has a relatively comfortable obligation-to-income ratio, as indicated by their Banking FOIR, which stands at 0.0% and is classified as comfortable.
-The customer's tradeline portfolio consists of N=27 total tradelines, M=22 live tradelines, and P=5 closed tradelines. The portfolio features a mix of credit card (26 accounts) and personal loan (1 account) products, with sanctioned exposure totaling INR 72,48,130 and outstanding balances of INR 8,22,679 for the entire portfolio, and INR 3,11,925 for the personal loan product. The customer's credit utilization percentage is 9.0% for credit cards, indicating a relatively healthy balance. Overall, this synthesised summary suggests a low-risk profile, with stable financial management and a manageable credit portfolio.</t>
+          <t>The customer's tradeline portfolio consists of N=27 total tradelines, M=22 live tradelines, and P=5 closed tradelines. The portfolio features a mix of credit card (26 accounts) and personal loan (1 account) products, with sanctioned exposure totaling INR 72,48,130 and outstanding balances of INR 8,22,679 for the entire portfolio, and INR 3,11,925 for the personal loan product. The customer's credit utilization percentage is 9.0% for credit cards, indicating a relatively healthy balance.
+The customer has a low-risk profile, with no missed payments in the last 18 months and a trade-to-enquiry ratio of 40.00%. The credit card balance utilization is 8.97%, and the personal loan balance remaining is 53.46%, suggesting moderate but manageable debt levels. With minimal enquiry activity and a stable loan acquisition velocity, the customer's credit behavior indicates a low-risk profile.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -550,15 +552,10 @@
 The customer's behavioral features indicate a low-risk profile. The % Missed Payments Last 18M is 0.00%, indicating no missed payments, and the Trade-to-Enquiry Ratio (Unsec 24M) is 40.00%, which is within healthy limits. The CC Balance Utilization is 8.97%, and the PL Balance Remaining is 53.46%, with the latter being moderate but not concerning. The customer has a low enquiry activity, with Unsecured Enquiries Last 12M at 0, indicating minimal enquiry pressure. The Avg Interpurchase Time All Loans (24M) is 3.45 months, suggesting a relatively stable loan acquisition velocity. Overall, the customer's credit behavior suggests a low-risk profile.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>The customer's banking profile indicates a stable financial situation. Their monthly cash flow is characterized by an average net inflow of ₹18, with total inflows exceeding outflows by ₹37. The customer's key spending categories include self expenses at ₹48,000, other expenses at ₹27,300, and food and restaurant expenditures at ₹1,970. Additionally, the customer has a relatively comfortable obligation-to-income ratio, as indicated by their Banking FOIR, which stands at 0.0% and is classified as comfortable.
-There are no detected transaction events to report.</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>E.True_Salary &amp; Secondary</t>
+          <t>E.True_Salary &amp; Unknown</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -571,16 +568,26 @@
       <c r="N2" t="n">
         <v>0</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>68.5% / Unsec: 60.8%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Sanctioned exposure peaked at ₹66.6L in Feb 2025, led by CC (₹63.5L) and PL (₹3.1L). Current exposure stands at ₹64.1L (CC, PL active), down 4% from peak — trend stable.</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>785</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
         <is>
           <t>Unsecured sanction is 100% of total (INR 72,48,130 of INR 72,48,130)</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>reports/combined_698167220_report.html</t>
         </is>

--- a/reports/excel/698167220.xlsx
+++ b/reports/excel/698167220.xlsx
@@ -535,14 +535,23 @@
         <v>698167220</v>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>39,210 / Symed</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Salary</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>The customer's tradeline portfolio consists of N=27 total tradelines, M=22 live tradelines, and P=5 closed tradelines. The portfolio features a mix of credit card (26 accounts) and personal loan (1 account) products, with sanctioned exposure totaling INR 72,48,130 and outstanding balances of INR 8,22,679 for the entire portfolio, and INR 3,11,925 for the personal loan product. The customer's credit utilization percentage is 9.0% for credit cards, indicating a relatively healthy balance.
-The customer has a low-risk profile, with no missed payments in the last 18 months and a trade-to-enquiry ratio of 40.00%. The credit card balance utilization is 8.97%, and the personal loan balance remaining is 53.46%, suggesting moderate but manageable debt levels. With minimal enquiry activity and a stable loan acquisition velocity, the customer's credit behavior indicates a low-risk profile.</t>
+          <t>The customer's income and credit profile indicate a stable financial situation. The customer's average monthly net inflow is ₹18, with an average salary of ₹39,210 received in two transactions, totaling ₹78,428 per month from Symed. Their key spending categories include self expenses at ₹48,000, other expenses at ₹27,300, and food and restaurant bills at ₹1,970. The customer's monthly cash flow is characterized by a small net outflow of ₹391.
+The customer's tradeline portfolio consists of N=27 total tradelines, M=22 live tradelines, and P=5 closed tradelines. The portfolio features a mix of credit card (26 accounts) and personal loan (1 account) products, with sanctioned exposure totaling INR 72,48,130 and outstanding balances of INR 8,22,679 for the entire portfolio, and INR 3,11,925 for the personal loan product. The customer's credit utilization percentage is 9.0% for credit cards, indicating a relatively healthy balance. The customer has a low-risk profile, with no missed payments, minimal enquiry pressure, and stable loan acquisition velocity.
+Note: This is a synthesised summary based on automated banking and bureau analyses. Independent verification is recommended before final credit decisions.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -552,10 +561,15 @@
 The customer's behavioral features indicate a low-risk profile. The % Missed Payments Last 18M is 0.00%, indicating no missed payments, and the Trade-to-Enquiry Ratio (Unsec 24M) is 40.00%, which is within healthy limits. The CC Balance Utilization is 8.97%, and the PL Balance Remaining is 53.46%, with the latter being moderate but not concerning. The customer has a low enquiry activity, with Unsecured Enquiries Last 12M at 0, indicating minimal enquiry pressure. The Avg Interpurchase Time All Loans (24M) is 3.45 months, suggesting a relatively stable loan acquisition velocity. Overall, the customer's credit behavior suggests a low-risk profile.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>The customer's banking profile indicates a stable financial situation. Their average monthly net inflow is ₹18, and their total income from Symed amounts to ₹78,428 per month, with an average salary of ₹39,210 received in two transactions. The customer's key spending categories include self expenses at ₹48,000, other expenses at ₹27,300, and food and restaurant bills at ₹1,970. Their monthly cash flow is characterized by a small net outflow of ₹391.
+The customer's banking profile also reveals some notable transaction patterns. In Jun 2025, the customer received ₹72,000 salary and transferred ₹72,000 to their own account the next day. In Jul 2025, the customer made two transactions worth ₹48,000 at CHINTAMALLA SAN, which is their most frequent merchant.</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>E.True_Salary &amp; Unknown</t>
+          <t>E.True_Salary &amp; Secondary</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>

--- a/reports/excel/698167220.xlsx
+++ b/reports/excel/698167220.xlsx
@@ -537,7 +537,7 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>39,210 / Symed</t>
+          <t>51,020 / Salary</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -549,9 +549,8 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>The customer's income and credit profile indicate a stable financial situation. The customer's average monthly net inflow is ₹18, with an average salary of ₹39,210 received in two transactions, totaling ₹78,428 per month from Symed. Their key spending categories include self expenses at ₹48,000, other expenses at ₹27,300, and food and restaurant bills at ₹1,970. The customer's monthly cash flow is characterized by a small net outflow of ₹391.
-The customer's tradeline portfolio consists of N=27 total tradelines, M=22 live tradelines, and P=5 closed tradelines. The portfolio features a mix of credit card (26 accounts) and personal loan (1 account) products, with sanctioned exposure totaling INR 72,48,130 and outstanding balances of INR 8,22,679 for the entire portfolio, and INR 3,11,925 for the personal loan product. The customer's credit utilization percentage is 9.0% for credit cards, indicating a relatively healthy balance. The customer has a low-risk profile, with no missed payments, minimal enquiry pressure, and stable loan acquisition velocity.
-Note: This is a synthesised summary based on automated banking and bureau analyses. Independent verification is recommended before final credit decisions.</t>
+          <t>The customer's income and credit profile indicate an average monthly cash flow of ₹50,922, with an average net inflow of ₹313,622 and outflow of ₹8,090. Their salary income is ₹51,020 on average from six transactions, while their EMI commitments amount to ₹7,500 per payment, with two debit transactions occurring each month. The customer's key spending categories include other expenses at ₹8,045 and mobility costs at ₹45.
+The customer's tradeline portfolio consists of N=27 total tradelines, M=22 live tradelines, and P=5 closed tradelines. The portfolio features a mix of credit card (26 accounts) and personal loan (1 account) products, with sanctioned exposure totaling INR 72,48,130 and outstanding balances of INR 8,22,679 for the entire portfolio, and INR 3,11,925 for the personal loan product. The customer's credit utilization percentage is 9.0% for credit cards, indicating a relatively healthy balance. The customer has a low-risk profile, with no missed payments, minimal enquiry pressure, and stable loan acquisition velocity.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -563,13 +562,13 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>The customer's banking profile indicates a stable financial situation. Their average monthly net inflow is ₹18, and their total income from Symed amounts to ₹78,428 per month, with an average salary of ₹39,210 received in two transactions. The customer's key spending categories include self expenses at ₹48,000, other expenses at ₹27,300, and food and restaurant bills at ₹1,970. Their monthly cash flow is characterized by a small net outflow of ₹391.
-The customer's banking profile also reveals some notable transaction patterns. In Jun 2025, the customer received ₹72,000 salary and transferred ₹72,000 to their own account the next day. In Jul 2025, the customer made two transactions worth ₹48,000 at CHINTAMALLA SAN, which is their most frequent merchant.</t>
+          <t>The customer's banking profile indicates a monthly cash flow of ₹50,922, with an average net inflow of ₹313,622 and outflow of ₹8,090. Their salary income is ₹51,020 on average from six transactions, while their EMI commitments amount to ₹7,500 per payment, with two debit transactions occurring each month. The customer's key spending categories include other expenses at ₹8,045 and mobility costs at ₹45.
+The customer received a salary of ₹72,000 in Jun 2025 and transferred ₹72,000 to their own account the next day. In Jul 2025, the customer made four transactions with BHOSALE RAJU TA, totaling ₹800. In Aug 2025, the customer received ₹51,020 from their salary income and paid ₹7,500 in EMI.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>E.True_Salary &amp; Secondary</t>
+          <t>E.True_Salary &amp; Primary</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>

--- a/reports/excel/698167220.xlsx
+++ b/reports/excel/698167220.xlsx
@@ -549,21 +549,22 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>The customer's income and credit profile indicate an average monthly cash flow of ₹50,922, with an average net inflow of ₹313,622 and outflow of ₹8,090. Their salary income is ₹51,020 on average from six transactions, while their EMI commitments amount to ₹7,500 per payment, with two debit transactions occurring each month. The customer's key spending categories include other expenses at ₹8,045 and mobility costs at ₹45.
-The customer's tradeline portfolio consists of N=27 total tradelines, M=22 live tradelines, and P=5 closed tradelines. The portfolio features a mix of credit card (26 accounts) and personal loan (1 account) products, with sanctioned exposure totaling INR 72,48,130 and outstanding balances of INR 8,22,679 for the entire portfolio, and INR 3,11,925 for the personal loan product. The customer's credit utilization percentage is 9.0% for credit cards, indicating a relatively healthy balance. The customer has a low-risk profile, with no missed payments, minimal enquiry pressure, and stable loan acquisition velocity.</t>
+          <t>The customer's income is ₹51,020 per month, sourced from six transactions, resulting in an average net cash flow of ₹50,922. Their key spending categories include other expenses at ₹8,045 and mobility costs at ₹45. The customer has EMI commitments averaging ₹7,500 per payment, with two debit transactions per month.
+The customer's tradeline portfolio consists of N=27 total tradelines (M live=22, P closed=5). The portfolio features a mix of loan products, with Credit Card being the dominant product type, accounting for 26 live accounts. Total sanctioned exposure stands at INR 72,48,130, while total outstanding is INR 8,22,679. Unsecured sanction amount and outstanding are identical to total outstanding, indicating no separation between secured and unsecured loans. The credit card utilization percentage is 9.0%, which is elevated. The customer's creditworthiness assessment is cautious.
+Note: This is a synthesised summary based on automated banking and bureau analyses. Independent verification is recommended before final credit decisions.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Here is the executive summary:
-The customer's tradeline portfolio consists of N=27 total tradelines, M=22 live tradelines, and P=5 closed tradelines. The portfolio features a mix of credit card (26 accounts) and personal loan (1 account) products, with sanctioned exposure totaling INR 72,48,130 and outstanding balances of INR 8,22,679 for the entire portfolio, and INR 3,11,925 for the personal loan product. The customer's credit utilization percentage is 9.0% for credit cards, indicating a relatively healthy balance. Notably, there are no DPD values above zero, suggesting a clean payment history.
-The customer's behavioral features indicate a low-risk profile. The % Missed Payments Last 18M is 0.00%, indicating no missed payments, and the Trade-to-Enquiry Ratio (Unsec 24M) is 40.00%, which is within healthy limits. The CC Balance Utilization is 8.97%, and the PL Balance Remaining is 53.46%, with the latter being moderate but not concerning. The customer has a low enquiry activity, with Unsecured Enquiries Last 12M at 0, indicating minimal enquiry pressure. The Avg Interpurchase Time All Loans (24M) is 3.45 months, suggesting a relatively stable loan acquisition velocity. Overall, the customer's credit behavior suggests a low-risk profile.</t>
+The customer's tradeline portfolio consists of N=27 total tradelines (M live=22, P closed=5). The portfolio features a mix of loan products, with Credit Card being the dominant product type, accounting for 26 live accounts. Total sanctioned exposure stands at INR 72,48,130, while total outstanding is INR 8,22,679. Unsecured sanction amount and outstanding are identical to total outstanding, indicating no separation between secured and unsecured loans. The credit card utilization percentage is 9.0%, which is elevated. There are no defaulted loan types present in the data.
+The customer's behavioral features indicate a relatively clean repayment profile, with zero DPD across all products and windows, no missed payments. The trade-to-enquiry ratio is 40.00% for unsecured trades, indicating moderate enquiry activity. Loan acquisition velocity is also notable, with an average interpurchase time of 3.45 months. However, the sanctioned exposure trend shows a decrease in sanctioned exposure over the past 12 and 6 months, from ₹66.6L to ₹64.1L and ₹66.6L to ₹64.3L respectively, indicating some stability in the trend.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>The customer's banking profile indicates a monthly cash flow of ₹50,922, with an average net inflow of ₹313,622 and outflow of ₹8,090. Their salary income is ₹51,020 on average from six transactions, while their EMI commitments amount to ₹7,500 per payment, with two debit transactions occurring each month. The customer's key spending categories include other expenses at ₹8,045 and mobility costs at ₹45.
-The customer received a salary of ₹72,000 in Jun 2025 and transferred ₹72,000 to their own account the next day. In Jul 2025, the customer made four transactions with BHOSALE RAJU TA, totaling ₹800. In Aug 2025, the customer received ₹51,020 from their salary income and paid ₹7,500 in EMI.</t>
+          <t>The customer's banking profile presents a stable financial picture. Their average monthly salary is ₹51,020, sourced from six transactions, resulting in an average net cash flow of ₹50,922. This translates to a total inflow of ₹313,622 and an outflow of ₹8,090 per month. The customer's key spending categories include other expenses at ₹8,045 and mobility costs at ₹45. Additionally, the customer has EMI commitments averaging ₹7,500 per payment, with two debit transactions per month.
+The customer's banking profile also reveals some notable merchant activity. The most frequent merchant is BHOSALE RAJU TA, with four transactions totaling ₹800. Furthermore, the account appears to be their primary account, as EMI payments are visible and average two debit transactions per month. Notably, the customer has a Banking FOIR obligation-to-income ratio of 14.7%, which falls within the comfortable range.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">

--- a/reports/excel/698167220.xlsx
+++ b/reports/excel/698167220.xlsx
@@ -546,12 +546,15 @@
           <t>Salary</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ongoing (2 months): Ongoing (2 months): EMI payment debit — avg ₹3,750/month (MB:SENT MONEY TO OWN 2411726562/EMI VEHICLE) ₹3,750</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>The customer's income is ₹51,020 per month, sourced from six transactions, resulting in an average net cash flow of ₹50,922. Their key spending categories include other expenses at ₹8,045 and mobility costs at ₹45. The customer has EMI commitments averaging ₹7,500 per payment, with two debit transactions per month.
-The customer's tradeline portfolio consists of N=27 total tradelines (M live=22, P closed=5). The portfolio features a mix of loan products, with Credit Card being the dominant product type, accounting for 26 live accounts. Total sanctioned exposure stands at INR 72,48,130, while total outstanding is INR 8,22,679. Unsecured sanction amount and outstanding are identical to total outstanding, indicating no separation between secured and unsecured loans. The credit card utilization percentage is 9.0%, which is elevated. The customer's creditworthiness assessment is cautious.
-Note: This is a synthesised summary based on automated banking and bureau analyses. Independent verification is recommended before final credit decisions.</t>
+          <t>The customer's income is ₹51,020 per month, with an average net inflow of ₹313,622 and outflow of ₹8,090 over a period. Key spending categories include "other" at ₹8,045 and Mobility at ₹45. The customer has EMI commitments averaging ₹7,500 per payment, with two debit transactions per month.
+The customer's tradeline portfolio consists of N=27 total tradelines (M live=22, P closed=5), featuring a mix of loan products, primarily Credit Card. Total sanctioned exposure stands at INR 72,48,130, while total outstanding is INR 8,22,679. Unsecured sanction amount and outstanding are identical to total outstanding, indicating no separation between secured and unsecured loans. The credit card utilization percentage is 9.0%, which is elevated. The customer's creditworthiness assessment is cautious due to the high risk profile indicated by their credit portfolio.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -563,8 +566,9 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>The customer's banking profile presents a stable financial picture. Their average monthly salary is ₹51,020, sourced from six transactions, resulting in an average net cash flow of ₹50,922. This translates to a total inflow of ₹313,622 and an outflow of ₹8,090 per month. The customer's key spending categories include other expenses at ₹8,045 and mobility costs at ₹45. Additionally, the customer has EMI commitments averaging ₹7,500 per payment, with two debit transactions per month.
-The customer's banking profile also reveals some notable merchant activity. The most frequent merchant is BHOSALE RAJU TA, with four transactions totaling ₹800. Furthermore, the account appears to be their primary account, as EMI payments are visible and average two debit transactions per month. Notably, the customer has a Banking FOIR obligation-to-income ratio of 14.7%, which falls within the comfortable range.</t>
+          <t>The customer's banking profile indicates a stable financial situation. The average monthly salary is ₹51,020, with six transactions throughout the period, resulting in an average net income of ₹8,045 per month. This translates to a total inflow of ₹313,622 and an outflow of ₹8,090 over the same period. Key spending categories include "other" at ₹8,045 and Mobility at ₹45. The customer has EMI commitments averaging ₹7,500 per payment, with two debit transactions per month.
+The customer's banking profile also shows a significant presence of BHOSALE RAJU TA as their most frequent merchant, with four transactions totaling ₹800. Additionally, the account appears to be primary, as EMI payments are visible, and there is an average of two debit transactions per month. The obligation-to-income ratio stands at 14.7%, which falls within the comfortable range.
+The customer has experienced several transaction events over the past two months. In Jun 2025, the customer received ₹72,000 salary and transferred ₹72,000 to their own account the next day. In Jul 2025, the customer made an EMI payment debit of ₹3,750.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">

--- a/reports/excel/698167220.xlsx
+++ b/reports/excel/698167220.xlsx
@@ -553,8 +553,8 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>The customer's income is ₹51,020 per month, with an average net inflow of ₹313,622 and outflow of ₹8,090 over a period. Key spending categories include "other" at ₹8,045 and Mobility at ₹45. The customer has EMI commitments averaging ₹7,500 per payment, with two debit transactions per month.
-The customer's tradeline portfolio consists of N=27 total tradelines (M live=22, P closed=5), featuring a mix of loan products, primarily Credit Card. Total sanctioned exposure stands at INR 72,48,130, while total outstanding is INR 8,22,679. Unsecured sanction amount and outstanding are identical to total outstanding, indicating no separation between secured and unsecured loans. The credit card utilization percentage is 9.0%, which is elevated. The customer's creditworthiness assessment is cautious due to the high risk profile indicated by their credit portfolio.</t>
+          <t>The customer's income is ₹313,622 per month, sourced from six salary transactions averaging ₹51,020 each. The average monthly cash flow indicates an inflow of ₹50,922 and outflow of ₹8,090, resulting in a net positive balance of ₹42,832. Key spending categories include mobility expenses at 45% of the total expenditure, with EMI commitments averaging ₹7,500 per payment.
+The customer's tradeline portfolio consists of N=27 total tradelines (M live=22, P closed=5), featuring a mix of loan products, primarily Credit Card accounts. Total sanctioned exposure stands at INR 72,48,130, while total outstanding is INR 8,22,679. Unsecured sanction amount and outstanding are identical to total outstanding, indicating no separation between secured and unsecured loans. The credit card utilization percentage is 9.0%, which is elevated. The customer's creditworthiness assessment is cautious due to the high risk profile indicated by their credit portfolio.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -566,9 +566,9 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>The customer's banking profile indicates a stable financial situation. The average monthly salary is ₹51,020, with six transactions throughout the period, resulting in an average net income of ₹8,045 per month. This translates to a total inflow of ₹313,622 and an outflow of ₹8,090 over the same period. Key spending categories include "other" at ₹8,045 and Mobility at ₹45. The customer has EMI commitments averaging ₹7,500 per payment, with two debit transactions per month.
-The customer's banking profile also shows a significant presence of BHOSALE RAJU TA as their most frequent merchant, with four transactions totaling ₹800. Additionally, the account appears to be primary, as EMI payments are visible, and there is an average of two debit transactions per month. The obligation-to-income ratio stands at 14.7%, which falls within the comfortable range.
-The customer has experienced several transaction events over the past two months. In Jun 2025, the customer received ₹72,000 salary and transferred ₹72,000 to their own account the next day. In Jul 2025, the customer made an EMI payment debit of ₹3,750.</t>
+          <t>The customer's banking profile presents a stable financial picture. The average monthly cash flow indicates an inflow of ₹50,922 and outflow of ₹8,090, resulting in a net positive balance of ₹42,832. This is supported by a total income of ₹313,622 from six salary transactions, with the average amount being ₹51,020 per month. Key spending categories include mobility expenses at 45% of the total expenditure, with EMI commitments averaging ₹7,500 per payment.
+The customer's banking profile also reveals a primary account, as evidenced by the visibility of EMI payments and an average of two debit transactions per month. The most frequent merchant is BHOSALE RAJU TA, with four transactions totaling ₹200. Notably, the customer has been making regular EMI payments, with an average amount of ₹3,750 per month.
+In Jun 2025, the customer received ₹72,000 salary and transferred ₹72,000 to their own account the next day. In Jul 2025, the customer made a payment of ₹7,500 for EMI.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">

--- a/reports/excel/698167220.xlsx
+++ b/reports/excel/698167220.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/reports/excel/698167220.xlsx
+++ b/reports/excel/698167220.xlsx
@@ -553,8 +553,8 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>The customer's income is ₹313,622 per month, sourced from six salary transactions averaging ₹51,020 each. The average monthly cash flow indicates an inflow of ₹50,922 and outflow of ₹8,090, resulting in a net positive balance of ₹42,832. Key spending categories include mobility expenses at 45% of the total expenditure, with EMI commitments averaging ₹7,500 per payment.
-The customer's tradeline portfolio consists of N=27 total tradelines (M live=22, P closed=5), featuring a mix of loan products, primarily Credit Card accounts. Total sanctioned exposure stands at INR 72,48,130, while total outstanding is INR 8,22,679. Unsecured sanction amount and outstanding are identical to total outstanding, indicating no separation between secured and unsecured loans. The credit card utilization percentage is 9.0%, which is elevated. The customer's creditworthiness assessment is cautious due to the high risk profile indicated by their credit portfolio.</t>
+          <t>The customer's income profile indicates a stable financial picture. The customer's salary income averages ₹51,020 per month from six transactions, contributing significantly to their average monthly cash flow of ₹50,922 and outflow of ₹8,090, resulting in a net positive balance of ₹42,832. The customer has established relationships with EMI EV and EMI VEHICLE, which receive debit transactions of ₹5,000 and ₹2,500, respectively.
+The customer's credit portfolio features 27 total tradelines (M live=22, P closed=5), primarily consisting of Credit Card loan products. Total sanctioned exposure stands at INR 72,48,130, while total outstanding is INR 8,22,679. Unsecured sanction amount and outstanding are identical to total outstanding, indicating no separation between secured and unsecured loans. The credit card utilization percentage is 9.0%, which is elevated. A cautious assessment of the customer's creditworthiness is warranted due to their high debt servicing ratio and elevated credit utilization.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -566,9 +566,9 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>The customer's banking profile presents a stable financial picture. The average monthly cash flow indicates an inflow of ₹50,922 and outflow of ₹8,090, resulting in a net positive balance of ₹42,832. This is supported by a total income of ₹313,622 from six salary transactions, with the average amount being ₹51,020 per month. Key spending categories include mobility expenses at 45% of the total expenditure, with EMI commitments averaging ₹7,500 per payment.
-The customer's banking profile also reveals a primary account, as evidenced by the visibility of EMI payments and an average of two debit transactions per month. The most frequent merchant is BHOSALE RAJU TA, with four transactions totaling ₹200. Notably, the customer has been making regular EMI payments, with an average amount of ₹3,750 per month.
-In Jun 2025, the customer received ₹72,000 salary and transferred ₹72,000 to their own account the next day. In Jul 2025, the customer made a payment of ₹7,500 for EMI.</t>
+          <t>The customer's banking profile presents a stable financial picture. The average monthly cash flow indicates an inflow of ₹50,922 and outflow of ₹8,090, resulting in a net positive balance of ₹42,832. This is largely driven by the customer's salary income, which averages ₹51,020 per month from six transactions. The EMI commitments of ₹7,500 per payment, with two debit transactions, contribute to the overall cash flow. Notably, the banking FOIR ratio stands at 14.7%, indicating a comfortable level of debt servicing.
+The customer's merchant behavior is characterized by regular interactions with BHOSALE RAJU TA, who receives four transactions worth ₹200 each. The most frequent merchant, BHOSALE RAJU TA, has been visited four times in the recent period. Additionally, the customer has established relationships with EMI EV and EMI VEHICLE, which receive debit transactions of ₹5,000 and ₹2,500, respectively. These merchants account for a significant proportion of the customer's spending, with Salary Oct 2025 accounts for 98% of credits and EMI EV accounts for 62% of debits.
+The customer has experienced several transaction events in recent months. In Jun 2025, the customer received ₹72,000 salary and transferred ₹72,000 to their own account the next day. In Jul 2025, the customer made an EMI payment debit of ₹3,750 (MB:SENT MONEY TO OWN 2411726562/EMI VEHICLE). The customer has also received payments from emerging merchants such as REKHA KANSAL and SALIM AMIN ATTA in recent months.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">

--- a/reports/excel/698167220.xlsx
+++ b/reports/excel/698167220.xlsx
@@ -553,15 +553,15 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>The customer's income profile indicates a stable financial picture. The customer's salary income averages ₹51,020 per month from six transactions, contributing significantly to their average monthly cash flow of ₹50,922 and outflow of ₹8,090, resulting in a net positive balance of ₹42,832. The customer has established relationships with EMI EV and EMI VEHICLE, which receive debit transactions of ₹5,000 and ₹2,500, respectively.
-The customer's credit portfolio features 27 total tradelines (M live=22, P closed=5), primarily consisting of Credit Card loan products. Total sanctioned exposure stands at INR 72,48,130, while total outstanding is INR 8,22,679. Unsecured sanction amount and outstanding are identical to total outstanding, indicating no separation between secured and unsecured loans. The credit card utilization percentage is 9.0%, which is elevated. A cautious assessment of the customer's creditworthiness is warranted due to their high debt servicing ratio and elevated credit utilization.</t>
+          <t>The customer's income profile indicates a stable financial picture. The customer's salary income averages ₹51,020 per month from six transactions, resulting in an average monthly cash flow of ₹50,922 and outflow of ₹8,090, with a net positive balance of ₹42,832. The customer has established relationships with EMI EV and EMI VEHICLE, which receive debit transactions of ₹5,000 and ₹2,500, respectively.
+The customer's tradeline portfolio consists of N=27 total tradelines (M live=22, P closed=5), featuring a mix of loan products, with Credit Card being the dominant product type. Total sanctioned exposure stands at INR 72,48,130, while total outstanding is INR 8,22,679. Unsecured sanction amount and outstanding are identical to total outstanding, indicating no separation between secured and unsecured loans. The credit card utilization percentage is 9.0%, which is elevated. The customer's creditworthiness assessment is cautious due to the high FOIR (total) of 68.5% and elevated credit card utilization.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Here is the executive summary:
-The customer's tradeline portfolio consists of N=27 total tradelines (M live=22, P closed=5). The portfolio features a mix of loan products, with Credit Card being the dominant product type, accounting for 26 live accounts. Total sanctioned exposure stands at INR 72,48,130, while total outstanding is INR 8,22,679. Unsecured sanction amount and outstanding are identical to total outstanding, indicating no separation between secured and unsecured loans. The credit card utilization percentage is 9.0%, which is elevated. There are no defaulted loan types present in the data.
-The customer's behavioral features indicate a relatively clean repayment profile, with zero DPD across all products and windows, no missed payments. The trade-to-enquiry ratio is 40.00% for unsecured trades, indicating moderate enquiry activity. Loan acquisition velocity is also notable, with an average interpurchase time of 3.45 months. However, the sanctioned exposure trend shows a decrease in sanctioned exposure over the past 12 and 6 months, from ₹66.6L to ₹64.1L and ₹66.6L to ₹64.3L respectively, indicating some stability in the trend.</t>
+The customer's tradeline portfolio consists of N=27 total tradelines (M live=22, P closed=5). The portfolio features a mix of loan products, with Credit Card being the dominant product type. Total sanctioned exposure stands at INR 72,48,130, while total outstanding is INR 8,22,679. Unsecured sanction amount and outstanding are identical to total outstanding, indicating no separation between secured and unsecured loans. The credit card utilization percentage is 9.0%, which is elevated. There are no defaulted loan types present in the data.
+The customer's behavioral features indicate a relatively clean repayment profile, with zero DPD across all products and windows, no missed payments. The trade-to-enquiry ratio is 40.00% for unsecured trades, indicating moderate enquiry activity. Loan acquisition velocity is also notable, with an average interpurchase time of 3.45 months. However, the FOIR (total) stands at 68.5%, indicating over-leveraging, while the FOIR (unsecured only) is 60.8%. The sanctioned exposure trend has decreased by 4% over the last 12 months, from ₹66.6L to ₹64.1L, and by 3% over the last 6 months, from prior 6M avg ₹66.6L to recent 6M avg ₹64.3L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">

--- a/reports/excel/698167220.xlsx
+++ b/reports/excel/698167220.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/reports/excel/698167220.xlsx
+++ b/reports/excel/698167220.xlsx
@@ -1,37 +1,143 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+  <si>
+    <t>CRN</t>
+  </si>
+  <si>
+    <t>offer Amt</t>
+  </si>
+  <si>
+    <t>Salary Value &amp; Company</t>
+  </si>
+  <si>
+    <t>Assesement Strength &amp; Quality</t>
+  </si>
+  <si>
+    <t>Relationship</t>
+  </si>
+  <si>
+    <t>Event Detector</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>Bureau Brief</t>
+  </si>
+  <si>
+    <t>Banking Breif</t>
+  </si>
+  <si>
+    <t>Bu &amp; Banking Segment</t>
+  </si>
+  <si>
+    <t>Max DPD &amp; Product</t>
+  </si>
+  <si>
+    <t>CC Util</t>
+  </si>
+  <si>
+    <t>Enquiries</t>
+  </si>
+  <si>
+    <t>Payments Missed in l 18M</t>
+  </si>
+  <si>
+    <t>Foir</t>
+  </si>
+  <si>
+    <t>Exposure Commentary</t>
+  </si>
+  <si>
+    <t>TU Score</t>
+  </si>
+  <si>
+    <t>Transaction Red flag</t>
+  </si>
+  <si>
+    <t>Concerns</t>
+  </si>
+  <si>
+    <t>Intelligent Report</t>
+  </si>
+  <si>
+    <t>51,020 / Salary</t>
+  </si>
+  <si>
+    <t>Salary</t>
+  </si>
+  <si>
+    <t>Ongoing (2 months): Ongoing (2 months): EMI payment debit — avg ₹3,750/month (MB:SENT MONEY TO OWN 2411726562/EMI VEHICLE) ₹3,750</t>
+  </si>
+  <si>
+    <t>The customer's income profile indicates a stable financial picture. The customer's salary income averages ₹51,020 per month from six transactions, resulting in an average monthly cash flow of ₹50,922 and outflow of ₹8,090, with a net positive balance of ₹42,832. The customer has established relationships with EMI EV and EMI VEHICLE, which receive debit transactions of ₹5,000 and ₹2,500, respectively.
+The customer's tradeline portfolio consists of N=27 total tradelines (M live=22, P closed=5), featuring a mix of loan products, with Credit Card being the dominant product type. Total sanctioned exposure stands at INR 72,48,130, while total outstanding is INR 8,22,679. Unsecured sanction amount and outstanding are identical to total outstanding, indicating no separation between secured and unsecured loans. The credit card utilization percentage is 9.0%, which is elevated. The customer's creditworthiness assessment is cautious due to the high FOIR (total) of 68.5% and elevated credit card utilization.</t>
+  </si>
+  <si>
+    <t>Here is the executive summary:
+The customer's tradeline portfolio consists of N=27 total tradelines (M live=22, P closed=5). The portfolio features a mix of loan products, with Credit Card being the dominant product type. Total sanctioned exposure stands at INR 72,48,130, while total outstanding is INR 8,22,679. Unsecured sanction amount and outstanding are identical to total outstanding, indicating no separation between secured and unsecured loans. The credit card utilization percentage is 9.0%, which is elevated. There are no defaulted loan types present in the data.
+The customer's behavioral features indicate a relatively clean repayment profile, with zero DPD across all products and windows, no missed payments. The trade-to-enquiry ratio is 40.00% for unsecured trades, indicating moderate enquiry activity. Loan acquisition velocity is also notable, with an average interpurchase time of 3.45 months. However, the FOIR (total) stands at 68.5%, indicating over-leveraging, while the FOIR (unsecured only) is 60.8%. The sanctioned exposure trend has decreased by 4% over the last 12 months, from ₹66.6L to ₹64.1L, and by 3% over the last 6 months, from prior 6M avg ₹66.6L to recent 6M avg ₹64.3L.</t>
+  </si>
+  <si>
+    <t>The customer's banking profile presents a stable financial picture. The average monthly cash flow indicates an inflow of ₹50,922 and outflow of ₹8,090, resulting in a net positive balance of ₹42,832. This is largely driven by the customer's salary income, which averages ₹51,020 per month from six transactions. The EMI commitments of ₹7,500 per payment, with two debit transactions, contribute to the overall cash flow. Notably, the banking FOIR ratio stands at 14.7%, indicating a comfortable level of debt servicing.
+The customer's merchant behavior is characterized by regular interactions with BHOSALE RAJU TA, who receives four transactions worth ₹200 each. The most frequent merchant, BHOSALE RAJU TA, has been visited four times in the recent period. Additionally, the customer has established relationships with EMI EV and EMI VEHICLE, which receive debit transactions of ₹5,000 and ₹2,500, respectively. These merchants account for a significant proportion of the customer's spending, with Salary Oct 2025 accounts for 98% of credits and EMI EV accounts for 62% of debits.
+The customer has experienced several transaction events in recent months. In Jun 2025, the customer received ₹72,000 salary and transferred ₹72,000 to their own account the next day. In Jul 2025, the customer made an EMI payment debit of ₹3,750 (MB:SENT MONEY TO OWN 2411726562/EMI VEHICLE). The customer has also received payments from emerging merchants such as REKHA KANSAL and SALIM AMIN ATTA in recent months.</t>
+  </si>
+  <si>
+    <t>E.True_Salary &amp; Primary</t>
+  </si>
+  <si>
+    <t>68.5% / Unsec: 60.8%</t>
+  </si>
+  <si>
+    <t>Sanctioned exposure peaked at ₹66.6L in Feb 2025, led by CC (₹63.5L) and PL (₹3.1L). Current exposure stands at ₹64.1L (CC, PL active), down 4% from peak — trend stable.</t>
+  </si>
+  <si>
+    <t>Unsecured sanction is 100% of total (INR 72,48,130 of INR 72,48,130)</t>
+  </si>
+  <si>
+    <t>reports/combined_698167220_report.html</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +152,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,198 +468,123 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:T2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CRN</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>offer Amt</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Salary Value &amp; Company</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Assesement Strength &amp; Quality</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Relationship</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Event Detector</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Bureau Brief</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Banking Breif</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Bu &amp; Banking Segment</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Max DPD &amp; Product</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>CC Util</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Enquiries</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Payments Missed in l 18M</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Foir</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Exposure Commentary</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>TU Score</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Transaction Red flag</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Concerns</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Intelligent Report</t>
-        </is>
+    <row r="1" spans="1:20">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" spans="1:20">
+      <c r="A2">
         <v>698167220</v>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>51,020 / Salary</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Salary</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Ongoing (2 months): Ongoing (2 months): EMI payment debit — avg ₹3,750/month (MB:SENT MONEY TO OWN 2411726562/EMI VEHICLE) ₹3,750</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>The customer's income profile indicates a stable financial picture. The customer's salary income averages ₹51,020 per month from six transactions, resulting in an average monthly cash flow of ₹50,922 and outflow of ₹8,090, with a net positive balance of ₹42,832. The customer has established relationships with EMI EV and EMI VEHICLE, which receive debit transactions of ₹5,000 and ₹2,500, respectively.
-The customer's tradeline portfolio consists of N=27 total tradelines (M live=22, P closed=5), featuring a mix of loan products, with Credit Card being the dominant product type. Total sanctioned exposure stands at INR 72,48,130, while total outstanding is INR 8,22,679. Unsecured sanction amount and outstanding are identical to total outstanding, indicating no separation between secured and unsecured loans. The credit card utilization percentage is 9.0%, which is elevated. The customer's creditworthiness assessment is cautious due to the high FOIR (total) of 68.5% and elevated credit card utilization.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Here is the executive summary:
-The customer's tradeline portfolio consists of N=27 total tradelines (M live=22, P closed=5). The portfolio features a mix of loan products, with Credit Card being the dominant product type. Total sanctioned exposure stands at INR 72,48,130, while total outstanding is INR 8,22,679. Unsecured sanction amount and outstanding are identical to total outstanding, indicating no separation between secured and unsecured loans. The credit card utilization percentage is 9.0%, which is elevated. There are no defaulted loan types present in the data.
-The customer's behavioral features indicate a relatively clean repayment profile, with zero DPD across all products and windows, no missed payments. The trade-to-enquiry ratio is 40.00% for unsecured trades, indicating moderate enquiry activity. Loan acquisition velocity is also notable, with an average interpurchase time of 3.45 months. However, the FOIR (total) stands at 68.5%, indicating over-leveraging, while the FOIR (unsecured only) is 60.8%. The sanctioned exposure trend has decreased by 4% over the last 12 months, from ₹66.6L to ₹64.1L, and by 3% over the last 6 months, from prior 6M avg ₹66.6L to recent 6M avg ₹64.3L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>The customer's banking profile presents a stable financial picture. The average monthly cash flow indicates an inflow of ₹50,922 and outflow of ₹8,090, resulting in a net positive balance of ₹42,832. This is largely driven by the customer's salary income, which averages ₹51,020 per month from six transactions. The EMI commitments of ₹7,500 per payment, with two debit transactions, contribute to the overall cash flow. Notably, the banking FOIR ratio stands at 14.7%, indicating a comfortable level of debt servicing.
-The customer's merchant behavior is characterized by regular interactions with BHOSALE RAJU TA, who receives four transactions worth ₹200 each. The most frequent merchant, BHOSALE RAJU TA, has been visited four times in the recent period. Additionally, the customer has established relationships with EMI EV and EMI VEHICLE, which receive debit transactions of ₹5,000 and ₹2,500, respectively. These merchants account for a significant proportion of the customer's spending, with Salary Oct 2025 accounts for 98% of credits and EMI EV accounts for 62% of debits.
-The customer has experienced several transaction events in recent months. In Jun 2025, the customer received ₹72,000 salary and transferred ₹72,000 to their own account the next day. In Jul 2025, the customer made an EMI payment debit of ₹3,750 (MB:SENT MONEY TO OWN 2411726562/EMI VEHICLE). The customer has also received payments from emerging merchants such as REKHA KANSAL and SALIM AMIN ATTA in recent months.</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>E.True_Salary &amp; Primary</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2">
         <v>8.970000000000001</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2">
         <v>0</v>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>68.5% / Unsec: 60.8%</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Sanctioned exposure peaked at ₹66.6L in Feb 2025, led by CC (₹63.5L) and PL (₹3.1L). Current exposure stands at ₹64.1L (CC, PL active), down 4% from peak — trend stable.</t>
-        </is>
-      </c>
-      <c r="Q2" t="n">
+      <c r="O2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q2">
         <v>785</v>
       </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>Unsecured sanction is 100% of total (INR 72,48,130 of INR 72,48,130)</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>reports/combined_698167220_report.html</t>
-        </is>
+      <c r="S2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T2" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>